--- a/public/kk/downloads/customer-statement-hindi.xlsx
+++ b/public/kk/downloads/customer-statement-hindi.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="कैसे भरें" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="स्टेटमेंट" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="कैसे भरें" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="स्टेटमेंट" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'स्टेटमेंट'!$9:$9</definedName>
@@ -575,7 +575,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>खाते का स्टेटमेंट: MDG Services का फ़ॉर्मेट</t>
+          <t>पेट्रोल पंप के खाते का स्टेटमेंट: MDG Services का फ़ॉर्मेट</t>
         </is>
       </c>
     </row>
@@ -589,28 +589,28 @@
     <row r="4" ht="57" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>1. स्टेटमेंट शीट के ऊपर अपने कारोबार का नाम, ग्राहक का नाम, स्टेटमेंट की तारीख़, कौन-सी अवधि का है (कब से, कब तक) और शुरू का बकाया लिखें।</t>
+          <t>1. स्टेटमेंट शीट के ऊपर अपने पंप का नाम, ट्रांसपोर्टर का नाम, स्टेटमेंट की तारीख़, कौन-सी अवधि का है (कब से, कब तक) और शुरू का बकाया लिखें।</t>
         </is>
       </c>
     </row>
     <row r="5" ht="57" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2. शुरू का बकाया: अवधि की शुरुआत में ग्राहक पर आपका जितना बाकी था। दूसरा स्टेटमेंट बना रहे हों तो पिछले स्टेटमेंट का आख़िरी बकाया।</t>
+          <t>2. शुरू का बकाया: अवधि की शुरुआत में ट्रांसपोर्टर पर आपका जितना बाकी था। दूसरा स्टेटमेंट बना रहे हों तो पिछले स्टेटमेंट का आख़िरी बकाया।</t>
         </is>
       </c>
     </row>
     <row r="6" ht="74" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>3. अवधि की हर बिक्री और हर पेमेंट की एक लाइन, तारीख़ के क्रम में। तारीख़, बिल या पर्ची नंबर, गाड़ी या माल लेने वाला, और ब्योरा लिखें (बिक्री में माल और मात्रा; पेमेंट में कैसे मिला और UTR या चेक नंबर)।</t>
+          <t>3. अवधि की हर उधार की भराई और हर पेमेंट की एक लाइन, तारीख़ के क्रम में। तारीख़, बिल या पर्ची नंबर, गाड़ी नंबर, और ब्योरा लिखें (भराई में तेल और लीटर; पेमेंट में कैसे मिला और UTR या चेक नंबर)।</t>
         </is>
       </c>
     </row>
     <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>4. बिक्री 'उधार दिया (₹)' में जाती है। पेमेंट 'पैसे मिले (₹)' में जाता है। एक लाइन में दोनों नहीं।</t>
+          <t>4. भराई 'उधार दिया (₹)' में जाती है। पेमेंट 'पैसे मिले (₹)' में जाता है। एक लाइन में दोनों नहीं।</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
     <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>6. आख़िरी बकाया, ऊपर और टेबल के नीचे, वह रकम है जो अवधि के अंत में ग्राहक पर आपकी बाकी है।</t>
+          <t>6. आख़िरी बकाया, ऊपर और टेबल के नीचे, वह रकम है जो अवधि के अंत में ट्रांसपोर्टर पर आपकी बाकी है।</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
     <row r="12" ht="57" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>9. A4 पर छापें या PDF बनाएँ, और अपने WhatsApp से भेजें। ग्राहक से कहें कि जाँच ले, और 7 दिन के भीतर बताए कि ठीक है या क्या गलत लग रहा है।</t>
+          <t>9. A4 पर छापें या PDF बनाएँ, और अपने WhatsApp से भेजें। ट्रांसपोर्टर से कहें कि जाँच ले, और 7 दिन के भीतर बताए कि ठीक है या क्या गलत लग रहा है।</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
     <row r="19" ht="66" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>हमारा ऐप खाता कवच उधार की बिक्री और पेमेंट एक साझा खाते में रखता है: शुरुआती सेटिंग में माल जाने से पहले ग्राहक रिक्वेस्ट भेजता है, और फ़ोन के नेट पर आते ही हर लाइन दोनों तरफ़ दिखती है। mdgservices.in/hi/khata-kavach</t>
+          <t>हमारा ऐप खाता कवच पेट्रोल पंप की हर उधार की भराई और हर पेमेंट एक साझा खाते में रखता है: शुरुआती सेटिंग में हर गाड़ी भरने से पहले ट्रांसपोर्टर रिक्वेस्ट भेजता है, और फ़ोन के नेट पर आते ही हर लाइन दोनों तरफ़ दिखती है। mdgservices.in/hi/khata-kavach</t>
         </is>
       </c>
     </row>
@@ -731,12 +731,12 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>आपका कारोबार</t>
+          <t>आपका पंप</t>
         </is>
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>Sharma Traders (काल्पनिक)</t>
+          <t>Sharma Fuels (काल्पनिक)</t>
         </is>
       </c>
       <c r="D4" s="12" t="n"/>
@@ -753,7 +753,7 @@
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>ग्राहक</t>
+          <t>ट्रांसपोर्टर</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
-          <t>गाड़ी नंबर / माल लेने वाला</t>
+          <t>गाड़ी नंबर</t>
         </is>
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>ब्योरा (माल और मात्रा, या कैसे मिले और UTR / चेक नंबर)</t>
+          <t>ब्योरा (तेल और लीटर, या कैसे मिले और UTR / चेक नंबर)</t>
         </is>
       </c>
       <c r="E9" s="16" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="C11" s="21" t="inlineStr">
         <is>
-          <t>UP00 SH 1005</t>
+          <t>UP00 GT 2201</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="C12" s="21" t="inlineStr">
         <is>
-          <t>UP00 SH 1006</t>
+          <t>UP00 GT 2202</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -1542,12 +1542,12 @@
     <row r="68">
       <c r="A68" s="27" t="inlineStr">
         <is>
-          <t>कारोबार की ओर से: दस्तख़त और तारीख़</t>
+          <t>पंप की ओर से: दस्तख़त और तारीख़</t>
         </is>
       </c>
       <c r="D68" s="27" t="inlineStr">
         <is>
-          <t>ग्राहक की पुष्टि: नाम, दस्तख़त और तारीख़</t>
+          <t>ट्रांसपोर्टर की पुष्टि: नाम, दस्तख़त और तारीख़</t>
         </is>
       </c>
     </row>
